--- a/VerveStacks_UGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_UGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_UGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99FD2CC4-570E-4928-8C93-9107EDF5D51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25B3B7FC-C36E-4779-A1E8-D5DCF5B99981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="127">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -370,15 +370,15 @@
     <t>at grid node - w600689855-132</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
     <t>w212063751-220</t>
   </si>
   <si>
     <t>at grid node - w212063751-220</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
     <t>w584663033-400</t>
   </si>
   <si>
@@ -413,12 +413,6 @@
   </si>
   <si>
     <t>at grid node - w696954754-220</t>
-  </si>
-  <si>
-    <t>UG3-220</t>
-  </si>
-  <si>
-    <t>at grid node - UG3-220</t>
   </si>
   <si>
     <t>UG2-220</t>
@@ -869,13 +863,13 @@
         <v>87</v>
       </c>
       <c r="R11" t="s">
+        <v>91</v>
+      </c>
+      <c r="S11" t="s">
+        <v>92</v>
+      </c>
+      <c r="T11" t="s">
         <v>110</v>
-      </c>
-      <c r="S11" t="s">
-        <v>111</v>
-      </c>
-      <c r="T11" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -907,13 +901,13 @@
         <v>87</v>
       </c>
       <c r="R12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -945,13 +939,13 @@
         <v>87</v>
       </c>
       <c r="R13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="T13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -983,13 +977,13 @@
         <v>87</v>
       </c>
       <c r="R14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="T14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -1021,13 +1015,13 @@
         <v>87</v>
       </c>
       <c r="R15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="T15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -1059,13 +1053,13 @@
         <v>87</v>
       </c>
       <c r="R16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="T16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="7:20" x14ac:dyDescent="0.45">
@@ -1097,13 +1091,13 @@
         <v>87</v>
       </c>
       <c r="R17" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="S17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="T17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="7:20" x14ac:dyDescent="0.45">
@@ -1123,13 +1117,13 @@
         <v>87</v>
       </c>
       <c r="R18" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="S18" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="T18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="7:20" x14ac:dyDescent="0.45">
@@ -1149,13 +1143,13 @@
         <v>87</v>
       </c>
       <c r="R19" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="S19" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="T19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="7:20" x14ac:dyDescent="0.45">
@@ -1175,13 +1169,13 @@
         <v>87</v>
       </c>
       <c r="R20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
